--- a/docs/项目相关/GanttChart/甘特项目规划器.xlsx
+++ b/docs/项目相关/GanttChart/甘特项目规划器.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:11_{48362921-4F50-7F4B-AFC6-A780ADAA0D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7D265A9-D767-574C-9059-6AFC51637B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>项目规划器</t>
   </si>
@@ -50,84 +50,6 @@
   </si>
   <si>
     <t>活动</t>
-  </si>
-  <si>
-    <t>活动 01</t>
-  </si>
-  <si>
-    <t>活动 02</t>
-  </si>
-  <si>
-    <t>活动 03</t>
-  </si>
-  <si>
-    <t>活动 04</t>
-  </si>
-  <si>
-    <t>活动 05</t>
-  </si>
-  <si>
-    <t>活动 06</t>
-  </si>
-  <si>
-    <t>活动 07</t>
-  </si>
-  <si>
-    <t>活动 08</t>
-  </si>
-  <si>
-    <t>活动 09</t>
-  </si>
-  <si>
-    <t>活动 10</t>
-  </si>
-  <si>
-    <t>活动 11</t>
-  </si>
-  <si>
-    <t>活动 12</t>
-  </si>
-  <si>
-    <t>活动 13</t>
-  </si>
-  <si>
-    <t>活动 14</t>
-  </si>
-  <si>
-    <t>活动 15</t>
-  </si>
-  <si>
-    <t>活动 16</t>
-  </si>
-  <si>
-    <t>活动 17</t>
-  </si>
-  <si>
-    <t>活动 18</t>
-  </si>
-  <si>
-    <t>活动 19</t>
-  </si>
-  <si>
-    <t>活动 20</t>
-  </si>
-  <si>
-    <t>活动 21</t>
-  </si>
-  <si>
-    <t>活动 22</t>
-  </si>
-  <si>
-    <t>活动 23</t>
-  </si>
-  <si>
-    <t>活动 24</t>
-  </si>
-  <si>
-    <t>活动 25</t>
-  </si>
-  <si>
-    <t>活动 26</t>
   </si>
   <si>
     <t>计划开始时间</t>
@@ -215,6 +137,126 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
+  </si>
+  <si>
+    <t>项目启动会议 &amp; 需求澄清</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>技术栈与代码规范确认</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	Git 仓库创建与分支策略制定</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库 ERD 设计</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>公共基础库初始化</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>微服务划分方案</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户认证与授权微服务</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户资料/地址微服务</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>跑腿订单微服务</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>菜品/食堂数据微服务</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>推荐算法原型</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>前端脚手架搭建</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>全局状态管理与 API 封装</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>通用 UI 组件库</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>登录/注册页面 + 表单校验</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>个人资料 &amp; 地址管理页面</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>食堂 &amp; 菜品列表页</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>菜品详情页</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>推荐列表组件（首页热推）</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>跑腿发布页面（地点选择、报酬设置）</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>跑腿员接单面板 &amp; 状态轮询</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>管理员后台（审核跑腿员、报表）</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>单元测试编写</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>前端自动化测试</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>性能压测</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>CI/CD 流水线配置</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据初始化脚本 &amp; 演示数据种子</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计分析/埋点集成</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>灰度发布与正式上线</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>API 文档生成</t>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1081,26 +1123,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </right>
-        <bottom style="thin">
-          <color theme="7"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="0"/>
         </patternFill>
       </fill>
@@ -1209,6 +1231,26 @@
         <bottom style="thin">
           <color theme="0"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="-0.24994659260841701"/>
+        </right>
+        <bottom style="thin">
+          <color theme="7"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1464,11 +1506,11 @@
     <tabColor theme="7"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:BO30"/>
+  <dimension ref="B1:BO34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="3.1640625" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.1640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="15.5" style="17" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" style="17" customWidth="1"/>
     <col min="3" max="6" width="11.5" style="3" customWidth="1"/>
     <col min="7" max="7" width="15.5" style="19" customWidth="1"/>
     <col min="8" max="27" width="3.1640625" style="3"/>
@@ -1494,34 +1536,34 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="6" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="H2" s="7">
         <v>1</v>
       </c>
       <c r="J2" s="8"/>
       <c r="K2" s="29" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="L2" s="30"/>
       <c r="M2" s="31"/>
       <c r="N2" s="9"/>
       <c r="O2" s="29" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="P2" s="30"/>
       <c r="Q2" s="30"/>
       <c r="R2" s="31"/>
       <c r="S2" s="10"/>
       <c r="T2" s="22" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="U2" s="23"/>
       <c r="V2" s="23"/>
       <c r="W2" s="32"/>
       <c r="X2" s="11"/>
       <c r="Y2" s="22" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="Z2" s="23"/>
       <c r="AA2" s="23"/>
@@ -1529,7 +1571,7 @@
       <c r="AC2" s="32"/>
       <c r="AD2" s="12"/>
       <c r="AE2" s="22" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="AF2" s="23"/>
       <c r="AG2" s="23"/>
@@ -1544,22 +1586,22 @@
         <v>2</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="I3" s="14"/>
       <c r="J3" s="15"/>
@@ -1771,39 +1813,39 @@
     </row>
     <row r="5" spans="2:67" ht="30" customHeight="1">
       <c r="B5" s="17" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C5" s="18">
         <v>1</v>
       </c>
       <c r="D5" s="18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E5" s="18">
         <v>1</v>
       </c>
       <c r="F5" s="18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G5" s="19">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="2:67" ht="30" customHeight="1">
       <c r="B6" s="17" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C6" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="18">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="E6" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="18">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="G6" s="19">
         <v>1</v>
@@ -1811,159 +1853,155 @@
     </row>
     <row r="7" spans="2:67" ht="30" customHeight="1">
       <c r="B7" s="17" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C7" s="18">
         <v>2</v>
       </c>
       <c r="D7" s="18">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="E7" s="18">
         <v>2</v>
       </c>
       <c r="F7" s="18">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="G7" s="19">
-        <v>0.35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:67" ht="30" customHeight="1">
       <c r="B8" s="17" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C8" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="18">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E8" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G8" s="19">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:67" ht="30" customHeight="1">
       <c r="B9" s="17" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C9" s="18">
         <v>4</v>
       </c>
       <c r="D9" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" s="18">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G9" s="19">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:67" ht="30" customHeight="1">
       <c r="B10" s="17" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C10" s="18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="18">
         <v>4</v>
       </c>
       <c r="F10" s="18">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G10" s="19">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:67" ht="30" customHeight="1">
       <c r="B11" s="17" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C11" s="18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D11" s="18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="18">
-        <v>5</v>
-      </c>
-      <c r="F11" s="18">
-        <v>3</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F11" s="18"/>
       <c r="G11" s="19">
         <v>0.5</v>
       </c>
     </row>
     <row r="12" spans="2:67" ht="30" customHeight="1">
       <c r="B12" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="18">
         <v>10</v>
-      </c>
-      <c r="C12" s="18">
-        <v>5</v>
       </c>
       <c r="D12" s="18">
         <v>2</v>
       </c>
       <c r="E12" s="18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F12" s="18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G12" s="19">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:67" ht="30" customHeight="1">
       <c r="B13" s="17" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C13" s="18">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D13" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" s="18">
-        <v>5</v>
-      </c>
-      <c r="F13" s="18">
-        <v>6</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F13" s="18"/>
       <c r="G13" s="19">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14" spans="2:67" ht="30" customHeight="1">
       <c r="B14" s="17" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C14" s="18">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D14" s="18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E14" s="18">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F14" s="18">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G14" s="19">
         <v>1</v>
@@ -1971,87 +2009,75 @@
     </row>
     <row r="15" spans="2:67" ht="30" customHeight="1">
       <c r="B15" s="17" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C15" s="20">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D15" s="18">
-        <v>1</v>
-      </c>
-      <c r="E15" s="18">
-        <v>5</v>
-      </c>
-      <c r="F15" s="18">
-        <v>8</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
       <c r="G15" s="19">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:67" ht="30" customHeight="1">
       <c r="B16" s="17" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C16" s="18">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D16" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="18">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F16" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="30" customHeight="1">
       <c r="B17" s="17" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C17" s="18">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D17" s="18">
-        <v>6</v>
-      </c>
-      <c r="E17" s="18">
-        <v>9</v>
-      </c>
-      <c r="F17" s="18">
-        <v>7</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
       <c r="G17" s="19">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="30" customHeight="1">
       <c r="B18" s="17" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C18" s="18">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D18" s="18">
         <v>3</v>
       </c>
-      <c r="E18" s="18">
-        <v>9</v>
-      </c>
-      <c r="F18" s="18">
-        <v>1</v>
-      </c>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
       <c r="G18" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="30" customHeight="1">
       <c r="B19" s="17" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C19" s="18">
         <v>9</v>
@@ -2071,222 +2097,242 @@
     </row>
     <row r="20" spans="2:7" ht="30" customHeight="1">
       <c r="B20" s="17" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C20" s="18">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D20" s="18">
-        <v>5</v>
-      </c>
-      <c r="E20" s="18">
-        <v>10</v>
-      </c>
-      <c r="F20" s="18">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
       <c r="G20" s="19">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="30" customHeight="1">
       <c r="B21" s="17" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C21" s="18">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D21" s="18">
         <v>2</v>
       </c>
-      <c r="E21" s="18">
-        <v>11</v>
-      </c>
-      <c r="F21" s="18">
-        <v>5</v>
-      </c>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
       <c r="G21" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="30" customHeight="1">
       <c r="B22" s="17" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C22" s="18">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D22" s="18">
-        <v>6</v>
-      </c>
-      <c r="E22" s="18">
-        <v>12</v>
-      </c>
-      <c r="F22" s="18">
-        <v>7</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
       <c r="G22" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="30" customHeight="1">
       <c r="B23" s="17" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C23" s="18">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D23" s="18">
-        <v>1</v>
-      </c>
-      <c r="E23" s="18">
-        <v>12</v>
-      </c>
-      <c r="F23" s="18">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
       <c r="G23" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="30" customHeight="1">
       <c r="B24" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="18">
         <v>22</v>
       </c>
-      <c r="C24" s="18">
-        <v>14</v>
-      </c>
       <c r="D24" s="18">
-        <v>5</v>
-      </c>
-      <c r="E24" s="18">
-        <v>14</v>
-      </c>
-      <c r="F24" s="18">
-        <v>6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
       <c r="G24" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="30" customHeight="1">
       <c r="B25" s="17" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C25" s="18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D25" s="18">
-        <v>8</v>
-      </c>
-      <c r="E25" s="18">
-        <v>14</v>
-      </c>
-      <c r="F25" s="18">
         <v>2</v>
       </c>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="19">
-        <v>0.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="30" customHeight="1">
       <c r="B26" s="17" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C26" s="18">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D26" s="18">
-        <v>7</v>
-      </c>
-      <c r="E26" s="18">
-        <v>14</v>
-      </c>
-      <c r="F26" s="18">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="30" customHeight="1">
       <c r="B27" s="17" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C27" s="18">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D27" s="18">
-        <v>4</v>
-      </c>
-      <c r="E27" s="18">
-        <v>15</v>
-      </c>
-      <c r="F27" s="18">
-        <v>8</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="19">
-        <v>0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="30" customHeight="1">
       <c r="B28" s="17" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C28" s="18">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D28" s="18">
         <v>5</v>
       </c>
-      <c r="E28" s="18">
-        <v>15</v>
-      </c>
-      <c r="F28" s="18">
-        <v>3</v>
-      </c>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="19">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="30" customHeight="1">
       <c r="B29" s="17" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C29" s="18">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D29" s="18">
-        <v>8</v>
-      </c>
-      <c r="E29" s="18">
-        <v>15</v>
-      </c>
-      <c r="F29" s="18">
-        <v>5</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
       <c r="G29" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="30" customHeight="1">
       <c r="B30" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C30" s="18">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D30" s="18">
-        <v>28</v>
-      </c>
-      <c r="E30" s="18">
-        <v>16</v>
-      </c>
-      <c r="F30" s="18">
-        <v>30</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
       <c r="G30" s="19">
-        <v>0.5</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="30" customHeight="1">
+      <c r="B31" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="18">
+        <v>32</v>
+      </c>
+      <c r="D31" s="18">
+        <v>2</v>
+      </c>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="30" customHeight="1">
+      <c r="B32" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="18">
+        <v>34</v>
+      </c>
+      <c r="D32" s="18">
+        <v>3</v>
+      </c>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="30" customHeight="1">
+      <c r="B33" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="18">
+        <v>37</v>
+      </c>
+      <c r="D33" s="18">
+        <v>4</v>
+      </c>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="30" customHeight="1">
+      <c r="B34" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="18">
+        <v>41</v>
+      </c>
+      <c r="D34" s="18">
+        <v>1</v>
+      </c>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="19">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2304,39 +2350,39 @@
     <mergeCell ref="K2:M2"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
-  <conditionalFormatting sqref="B31:BO31">
+  <conditionalFormatting sqref="B35:BO35">
     <cfRule type="expression" dxfId="9" priority="2">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:BO4">
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>H$4=period_selected</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:BO30">
-    <cfRule type="expression" dxfId="8" priority="1">
+  <conditionalFormatting sqref="H5:BO34">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>完成百分比</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="3">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>PercentCompleteBeyond</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>实际值</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>ActualBeyond</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="3" priority="6">
       <formula>计划</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="7">
+    <cfRule type="expression" dxfId="2" priority="7">
       <formula>H$4=period_selected</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="11">
+    <cfRule type="expression" dxfId="1" priority="11">
       <formula>MOD(COLUMN(),2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="12">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
